--- a/エクセル検索webアプリ/input.xlsx
+++ b/エクセル検索webアプリ/input.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Data\repository\いろいろ交換\iroirokoukan\エクセル検索webアプリ\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D0E322A6-C683-4D7E-BAEA-5B5D2593EB17}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{059CE40E-DEAE-418E-881A-88DEB9EDD4AE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2306" uniqueCount="123">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2310" uniqueCount="125">
   <si>
     <t>(meta)</t>
   </si>
@@ -392,6 +392,14 @@
   </si>
   <si>
     <t>bb</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>fakdgjakjfjfksdjfkajf;jfksajfldjf;aksjf;lsjfeeafjea</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>a</t>
     <phoneticPr fontId="1"/>
   </si>
 </sst>
@@ -750,19 +758,19 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:AP89"/>
-  <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
+  <sheetFormatPr defaultRowHeight="13" x14ac:dyDescent="0.2"/>
   <sheetData>
-    <row r="1" spans="1:42" x14ac:dyDescent="0.15">
+    <row r="1" spans="1:42" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="2" spans="1:42" x14ac:dyDescent="0.15">
+    <row r="2" spans="1:42" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:42" x14ac:dyDescent="0.15">
+    <row r="3" spans="1:42" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>2</v>
       </c>
@@ -890,7 +898,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="4" spans="1:42" x14ac:dyDescent="0.15">
+    <row r="4" spans="1:42" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
         <v>7</v>
       </c>
@@ -1018,7 +1026,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="5" spans="1:42" x14ac:dyDescent="0.15">
+    <row r="5" spans="1:42" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
         <v>10</v>
       </c>
@@ -1146,7 +1154,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="6" spans="1:42" x14ac:dyDescent="0.15">
+    <row r="6" spans="1:42" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
         <v>12</v>
       </c>
@@ -1274,7 +1282,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="7" spans="1:42" x14ac:dyDescent="0.15">
+    <row r="7" spans="1:42" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
         <v>38</v>
       </c>
@@ -1402,7 +1410,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="8" spans="1:42" x14ac:dyDescent="0.15">
+    <row r="8" spans="1:42" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
         <v>39</v>
       </c>
@@ -1530,7 +1538,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="9" spans="1:42" x14ac:dyDescent="0.15">
+    <row r="9" spans="1:42" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
         <v>34</v>
       </c>
@@ -1658,7 +1666,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="10" spans="1:42" x14ac:dyDescent="0.15">
+    <row r="10" spans="1:42" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
         <v>41</v>
       </c>
@@ -1786,7 +1794,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="11" spans="1:42" x14ac:dyDescent="0.15">
+    <row r="11" spans="1:42" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
         <v>42</v>
       </c>
@@ -1914,7 +1922,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="12" spans="1:42" x14ac:dyDescent="0.15">
+    <row r="12" spans="1:42" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
         <v>35</v>
       </c>
@@ -2042,7 +2050,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="13" spans="1:42" x14ac:dyDescent="0.15">
+    <row r="13" spans="1:42" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
         <v>44</v>
       </c>
@@ -2170,7 +2178,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="14" spans="1:42" x14ac:dyDescent="0.15">
+    <row r="14" spans="1:42" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
         <v>45</v>
       </c>
@@ -2298,7 +2306,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="15" spans="1:42" x14ac:dyDescent="0.15">
+    <row r="15" spans="1:42" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
         <v>36</v>
       </c>
@@ -2426,7 +2434,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="16" spans="1:42" x14ac:dyDescent="0.15">
+    <row r="16" spans="1:42" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
         <v>47</v>
       </c>
@@ -2554,7 +2562,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="17" spans="1:42" x14ac:dyDescent="0.15">
+    <row r="17" spans="1:42" x14ac:dyDescent="0.2">
       <c r="A17" t="s">
         <v>48</v>
       </c>
@@ -2682,7 +2690,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="18" spans="1:42" x14ac:dyDescent="0.15">
+    <row r="18" spans="1:42" x14ac:dyDescent="0.2">
       <c r="A18" t="s">
         <v>37</v>
       </c>
@@ -2810,7 +2818,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="19" spans="1:42" x14ac:dyDescent="0.15">
+    <row r="19" spans="1:42" x14ac:dyDescent="0.2">
       <c r="A19" t="s">
         <v>50</v>
       </c>
@@ -2938,7 +2946,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="20" spans="1:42" x14ac:dyDescent="0.15">
+    <row r="20" spans="1:42" x14ac:dyDescent="0.2">
       <c r="A20" t="s">
         <v>51</v>
       </c>
@@ -3066,7 +3074,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="21" spans="1:42" x14ac:dyDescent="0.15">
+    <row r="21" spans="1:42" x14ac:dyDescent="0.2">
       <c r="A21" t="s">
         <v>40</v>
       </c>
@@ -3194,7 +3202,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="22" spans="1:42" x14ac:dyDescent="0.15">
+    <row r="22" spans="1:42" x14ac:dyDescent="0.2">
       <c r="A22" t="s">
         <v>53</v>
       </c>
@@ -3322,7 +3330,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="23" spans="1:42" x14ac:dyDescent="0.15">
+    <row r="23" spans="1:42" x14ac:dyDescent="0.2">
       <c r="A23" t="s">
         <v>54</v>
       </c>
@@ -3450,7 +3458,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="24" spans="1:42" x14ac:dyDescent="0.15">
+    <row r="24" spans="1:42" x14ac:dyDescent="0.2">
       <c r="A24" t="s">
         <v>43</v>
       </c>
@@ -3578,7 +3586,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="25" spans="1:42" x14ac:dyDescent="0.15">
+    <row r="25" spans="1:42" x14ac:dyDescent="0.2">
       <c r="A25" t="s">
         <v>56</v>
       </c>
@@ -3706,7 +3714,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="26" spans="1:42" x14ac:dyDescent="0.15">
+    <row r="26" spans="1:42" x14ac:dyDescent="0.2">
       <c r="A26" t="s">
         <v>57</v>
       </c>
@@ -3834,7 +3842,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="27" spans="1:42" x14ac:dyDescent="0.15">
+    <row r="27" spans="1:42" x14ac:dyDescent="0.2">
       <c r="A27" t="s">
         <v>46</v>
       </c>
@@ -3962,7 +3970,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="28" spans="1:42" x14ac:dyDescent="0.15">
+    <row r="28" spans="1:42" x14ac:dyDescent="0.2">
       <c r="A28" t="s">
         <v>59</v>
       </c>
@@ -4090,7 +4098,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="29" spans="1:42" x14ac:dyDescent="0.15">
+    <row r="29" spans="1:42" x14ac:dyDescent="0.2">
       <c r="A29" t="s">
         <v>60</v>
       </c>
@@ -4218,7 +4226,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="30" spans="1:42" x14ac:dyDescent="0.15">
+    <row r="30" spans="1:42" x14ac:dyDescent="0.2">
       <c r="A30" t="s">
         <v>49</v>
       </c>
@@ -4346,7 +4354,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="31" spans="1:42" x14ac:dyDescent="0.15">
+    <row r="31" spans="1:42" x14ac:dyDescent="0.2">
       <c r="A31" t="s">
         <v>62</v>
       </c>
@@ -4474,7 +4482,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="32" spans="1:42" x14ac:dyDescent="0.15">
+    <row r="32" spans="1:42" x14ac:dyDescent="0.2">
       <c r="A32" t="s">
         <v>63</v>
       </c>
@@ -4602,7 +4610,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="33" spans="1:42" x14ac:dyDescent="0.15">
+    <row r="33" spans="1:42" x14ac:dyDescent="0.2">
       <c r="A33" t="s">
         <v>52</v>
       </c>
@@ -4730,7 +4738,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="34" spans="1:42" x14ac:dyDescent="0.15">
+    <row r="34" spans="1:42" x14ac:dyDescent="0.2">
       <c r="A34" t="s">
         <v>65</v>
       </c>
@@ -4858,7 +4866,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="35" spans="1:42" x14ac:dyDescent="0.15">
+    <row r="35" spans="1:42" x14ac:dyDescent="0.2">
       <c r="A35" t="s">
         <v>66</v>
       </c>
@@ -4986,7 +4994,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="36" spans="1:42" x14ac:dyDescent="0.15">
+    <row r="36" spans="1:42" x14ac:dyDescent="0.2">
       <c r="A36" t="s">
         <v>55</v>
       </c>
@@ -5114,7 +5122,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="37" spans="1:42" x14ac:dyDescent="0.15">
+    <row r="37" spans="1:42" x14ac:dyDescent="0.2">
       <c r="A37" t="s">
         <v>68</v>
       </c>
@@ -5242,7 +5250,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="38" spans="1:42" x14ac:dyDescent="0.15">
+    <row r="38" spans="1:42" x14ac:dyDescent="0.2">
       <c r="A38" t="s">
         <v>69</v>
       </c>
@@ -5370,7 +5378,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="39" spans="1:42" x14ac:dyDescent="0.15">
+    <row r="39" spans="1:42" x14ac:dyDescent="0.2">
       <c r="A39" t="s">
         <v>58</v>
       </c>
@@ -5498,7 +5506,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="40" spans="1:42" x14ac:dyDescent="0.15">
+    <row r="40" spans="1:42" x14ac:dyDescent="0.2">
       <c r="A40" t="s">
         <v>71</v>
       </c>
@@ -5626,7 +5634,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="41" spans="1:42" x14ac:dyDescent="0.15">
+    <row r="41" spans="1:42" x14ac:dyDescent="0.2">
       <c r="A41" t="s">
         <v>72</v>
       </c>
@@ -5754,7 +5762,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="42" spans="1:42" x14ac:dyDescent="0.15">
+    <row r="42" spans="1:42" x14ac:dyDescent="0.2">
       <c r="A42" t="s">
         <v>61</v>
       </c>
@@ -5882,7 +5890,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="43" spans="1:42" x14ac:dyDescent="0.15">
+    <row r="43" spans="1:42" x14ac:dyDescent="0.2">
       <c r="A43" t="s">
         <v>74</v>
       </c>
@@ -6010,7 +6018,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="44" spans="1:42" x14ac:dyDescent="0.15">
+    <row r="44" spans="1:42" x14ac:dyDescent="0.2">
       <c r="A44" t="s">
         <v>75</v>
       </c>
@@ -6138,7 +6146,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="45" spans="1:42" x14ac:dyDescent="0.15">
+    <row r="45" spans="1:42" x14ac:dyDescent="0.2">
       <c r="A45" t="s">
         <v>64</v>
       </c>
@@ -6266,7 +6274,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="46" spans="1:42" x14ac:dyDescent="0.15">
+    <row r="46" spans="1:42" x14ac:dyDescent="0.2">
       <c r="A46" t="s">
         <v>77</v>
       </c>
@@ -6394,7 +6402,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="47" spans="1:42" x14ac:dyDescent="0.15">
+    <row r="47" spans="1:42" x14ac:dyDescent="0.2">
       <c r="A47" t="s">
         <v>78</v>
       </c>
@@ -6522,7 +6530,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="48" spans="1:42" x14ac:dyDescent="0.15">
+    <row r="48" spans="1:42" x14ac:dyDescent="0.2">
       <c r="A48" t="s">
         <v>67</v>
       </c>
@@ -6650,7 +6658,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="49" spans="1:42" x14ac:dyDescent="0.15">
+    <row r="49" spans="1:42" x14ac:dyDescent="0.2">
       <c r="A49" t="s">
         <v>80</v>
       </c>
@@ -6778,7 +6786,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="50" spans="1:42" x14ac:dyDescent="0.15">
+    <row r="50" spans="1:42" x14ac:dyDescent="0.2">
       <c r="A50" t="s">
         <v>81</v>
       </c>
@@ -6906,7 +6914,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="51" spans="1:42" x14ac:dyDescent="0.15">
+    <row r="51" spans="1:42" x14ac:dyDescent="0.2">
       <c r="A51" t="s">
         <v>70</v>
       </c>
@@ -7034,7 +7042,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="52" spans="1:42" x14ac:dyDescent="0.15">
+    <row r="52" spans="1:42" x14ac:dyDescent="0.2">
       <c r="A52" t="s">
         <v>83</v>
       </c>
@@ -7162,7 +7170,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="53" spans="1:42" x14ac:dyDescent="0.15">
+    <row r="53" spans="1:42" x14ac:dyDescent="0.2">
       <c r="A53" t="s">
         <v>84</v>
       </c>
@@ -7290,7 +7298,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="54" spans="1:42" x14ac:dyDescent="0.15">
+    <row r="54" spans="1:42" x14ac:dyDescent="0.2">
       <c r="A54" t="s">
         <v>73</v>
       </c>
@@ -7418,7 +7426,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="55" spans="1:42" x14ac:dyDescent="0.15">
+    <row r="55" spans="1:42" x14ac:dyDescent="0.2">
       <c r="A55" t="s">
         <v>86</v>
       </c>
@@ -7546,7 +7554,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="56" spans="1:42" x14ac:dyDescent="0.15">
+    <row r="56" spans="1:42" x14ac:dyDescent="0.2">
       <c r="A56" t="s">
         <v>87</v>
       </c>
@@ -7674,7 +7682,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="57" spans="1:42" x14ac:dyDescent="0.15">
+    <row r="57" spans="1:42" x14ac:dyDescent="0.2">
       <c r="A57" t="s">
         <v>76</v>
       </c>
@@ -7802,7 +7810,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="58" spans="1:42" x14ac:dyDescent="0.15">
+    <row r="58" spans="1:42" x14ac:dyDescent="0.2">
       <c r="A58" t="s">
         <v>89</v>
       </c>
@@ -7930,7 +7938,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="59" spans="1:42" x14ac:dyDescent="0.15">
+    <row r="59" spans="1:42" x14ac:dyDescent="0.2">
       <c r="A59" t="s">
         <v>90</v>
       </c>
@@ -8058,7 +8066,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="60" spans="1:42" x14ac:dyDescent="0.15">
+    <row r="60" spans="1:42" x14ac:dyDescent="0.2">
       <c r="A60" t="s">
         <v>79</v>
       </c>
@@ -8186,7 +8194,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="61" spans="1:42" x14ac:dyDescent="0.15">
+    <row r="61" spans="1:42" x14ac:dyDescent="0.2">
       <c r="A61" t="s">
         <v>92</v>
       </c>
@@ -8314,7 +8322,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="62" spans="1:42" x14ac:dyDescent="0.15">
+    <row r="62" spans="1:42" x14ac:dyDescent="0.2">
       <c r="A62" t="s">
         <v>93</v>
       </c>
@@ -8442,7 +8450,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="63" spans="1:42" x14ac:dyDescent="0.15">
+    <row r="63" spans="1:42" x14ac:dyDescent="0.2">
       <c r="A63" t="s">
         <v>82</v>
       </c>
@@ -8570,7 +8578,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="64" spans="1:42" x14ac:dyDescent="0.15">
+    <row r="64" spans="1:42" x14ac:dyDescent="0.2">
       <c r="A64" t="s">
         <v>95</v>
       </c>
@@ -8698,7 +8706,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="65" spans="1:42" x14ac:dyDescent="0.15">
+    <row r="65" spans="1:42" x14ac:dyDescent="0.2">
       <c r="A65" t="s">
         <v>96</v>
       </c>
@@ -8826,7 +8834,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="66" spans="1:42" x14ac:dyDescent="0.15">
+    <row r="66" spans="1:42" x14ac:dyDescent="0.2">
       <c r="A66" t="s">
         <v>85</v>
       </c>
@@ -8954,7 +8962,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="67" spans="1:42" x14ac:dyDescent="0.15">
+    <row r="67" spans="1:42" x14ac:dyDescent="0.2">
       <c r="A67" t="s">
         <v>98</v>
       </c>
@@ -9082,7 +9090,7 @@
         <v>98</v>
       </c>
     </row>
-    <row r="68" spans="1:42" x14ac:dyDescent="0.15">
+    <row r="68" spans="1:42" x14ac:dyDescent="0.2">
       <c r="A68" t="s">
         <v>99</v>
       </c>
@@ -9210,7 +9218,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="69" spans="1:42" x14ac:dyDescent="0.15">
+    <row r="69" spans="1:42" x14ac:dyDescent="0.2">
       <c r="A69" t="s">
         <v>88</v>
       </c>
@@ -9338,7 +9346,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="70" spans="1:42" x14ac:dyDescent="0.15">
+    <row r="70" spans="1:42" x14ac:dyDescent="0.2">
       <c r="A70" t="s">
         <v>101</v>
       </c>
@@ -9466,7 +9474,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="71" spans="1:42" x14ac:dyDescent="0.15">
+    <row r="71" spans="1:42" x14ac:dyDescent="0.2">
       <c r="A71" t="s">
         <v>102</v>
       </c>
@@ -9594,7 +9602,7 @@
         <v>102</v>
       </c>
     </row>
-    <row r="72" spans="1:42" x14ac:dyDescent="0.15">
+    <row r="72" spans="1:42" x14ac:dyDescent="0.2">
       <c r="A72" t="s">
         <v>91</v>
       </c>
@@ -9722,7 +9730,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="73" spans="1:42" x14ac:dyDescent="0.15">
+    <row r="73" spans="1:42" x14ac:dyDescent="0.2">
       <c r="A73" t="s">
         <v>104</v>
       </c>
@@ -9850,7 +9858,7 @@
         <v>104</v>
       </c>
     </row>
-    <row r="74" spans="1:42" x14ac:dyDescent="0.15">
+    <row r="74" spans="1:42" x14ac:dyDescent="0.2">
       <c r="A74" t="s">
         <v>105</v>
       </c>
@@ -9978,7 +9986,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="75" spans="1:42" x14ac:dyDescent="0.15">
+    <row r="75" spans="1:42" x14ac:dyDescent="0.2">
       <c r="A75" t="s">
         <v>94</v>
       </c>
@@ -10106,7 +10114,7 @@
         <v>106</v>
       </c>
     </row>
-    <row r="76" spans="1:42" x14ac:dyDescent="0.15">
+    <row r="76" spans="1:42" x14ac:dyDescent="0.2">
       <c r="A76" t="s">
         <v>107</v>
       </c>
@@ -10234,7 +10242,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="77" spans="1:42" x14ac:dyDescent="0.15">
+    <row r="77" spans="1:42" x14ac:dyDescent="0.2">
       <c r="A77" t="s">
         <v>108</v>
       </c>
@@ -10362,7 +10370,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="78" spans="1:42" x14ac:dyDescent="0.15">
+    <row r="78" spans="1:42" x14ac:dyDescent="0.2">
       <c r="A78" t="s">
         <v>97</v>
       </c>
@@ -10490,7 +10498,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="79" spans="1:42" x14ac:dyDescent="0.15">
+    <row r="79" spans="1:42" x14ac:dyDescent="0.2">
       <c r="A79" t="s">
         <v>110</v>
       </c>
@@ -10618,7 +10626,7 @@
         <v>110</v>
       </c>
     </row>
-    <row r="80" spans="1:42" x14ac:dyDescent="0.15">
+    <row r="80" spans="1:42" x14ac:dyDescent="0.2">
       <c r="A80" t="s">
         <v>111</v>
       </c>
@@ -10746,7 +10754,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="81" spans="1:42" x14ac:dyDescent="0.15">
+    <row r="81" spans="1:42" x14ac:dyDescent="0.2">
       <c r="A81" t="s">
         <v>100</v>
       </c>
@@ -10874,7 +10882,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="82" spans="1:42" x14ac:dyDescent="0.15">
+    <row r="82" spans="1:42" x14ac:dyDescent="0.2">
       <c r="A82" t="s">
         <v>113</v>
       </c>
@@ -11002,7 +11010,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="83" spans="1:42" x14ac:dyDescent="0.15">
+    <row r="83" spans="1:42" x14ac:dyDescent="0.2">
       <c r="A83" t="s">
         <v>114</v>
       </c>
@@ -11130,7 +11138,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="84" spans="1:42" x14ac:dyDescent="0.15">
+    <row r="84" spans="1:42" x14ac:dyDescent="0.2">
       <c r="A84" t="s">
         <v>103</v>
       </c>
@@ -11258,7 +11266,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="85" spans="1:42" x14ac:dyDescent="0.15">
+    <row r="85" spans="1:42" x14ac:dyDescent="0.2">
       <c r="A85" t="s">
         <v>116</v>
       </c>
@@ -11386,7 +11394,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="86" spans="1:42" x14ac:dyDescent="0.15">
+    <row r="86" spans="1:42" x14ac:dyDescent="0.2">
       <c r="A86" t="s">
         <v>117</v>
       </c>
@@ -11514,7 +11522,7 @@
         <v>117</v>
       </c>
     </row>
-    <row r="87" spans="1:42" x14ac:dyDescent="0.15">
+    <row r="87" spans="1:42" x14ac:dyDescent="0.2">
       <c r="A87" t="s">
         <v>106</v>
       </c>
@@ -11642,7 +11650,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="88" spans="1:42" x14ac:dyDescent="0.15">
+    <row r="88" spans="1:42" x14ac:dyDescent="0.2">
       <c r="A88" t="s">
         <v>119</v>
       </c>
@@ -11770,7 +11778,7 @@
         <v>119</v>
       </c>
     </row>
-    <row r="89" spans="1:42" x14ac:dyDescent="0.15">
+    <row r="89" spans="1:42" x14ac:dyDescent="0.2">
       <c r="A89" t="s">
         <v>120</v>
       </c>
@@ -11906,30 +11914,30 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:D9"/>
-  <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
+  <dimension ref="A1:E9"/>
+  <sheetFormatPr defaultRowHeight="13" x14ac:dyDescent="0.2"/>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.15">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.15">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.15">
+    <row r="3" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.15">
+    <row r="4" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.15">
+    <row r="5" spans="1:5" x14ac:dyDescent="0.2">
       <c r="B5" s="3" t="s">
         <v>20</v>
       </c>
@@ -11938,7 +11946,7 @@
       </c>
       <c r="D5" s="3"/>
     </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.15">
+    <row r="6" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
         <v>19</v>
       </c>
@@ -11949,8 +11957,11 @@
       <c r="D6" s="2" t="s">
         <v>122</v>
       </c>
+      <c r="E6" t="s">
+        <v>123</v>
+      </c>
     </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.15">
+    <row r="7" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
         <v>22</v>
       </c>
@@ -11963,8 +11974,11 @@
       <c r="D7">
         <v>410</v>
       </c>
+      <c r="E7" t="s">
+        <v>124</v>
+      </c>
     </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.15">
+    <row r="8" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
         <v>23</v>
       </c>
@@ -11977,8 +11991,11 @@
       <c r="D8">
         <v>305</v>
       </c>
+      <c r="E8" t="s">
+        <v>124</v>
+      </c>
     </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.15">
+    <row r="9" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
         <v>24</v>
       </c>
@@ -11990,6 +12007,9 @@
       </c>
       <c r="D9">
         <v>220</v>
+      </c>
+      <c r="E9" t="s">
+        <v>124</v>
       </c>
     </row>
   </sheetData>
@@ -12005,14 +12025,14 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:C5"/>
-  <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
+  <sheetFormatPr defaultRowHeight="13" x14ac:dyDescent="0.2"/>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>26</v>
       </c>
@@ -12023,7 +12043,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>29</v>
       </c>
@@ -12034,7 +12054,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
         <v>9</v>
       </c>
@@ -12045,7 +12065,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
         <v>14</v>
       </c>
